--- a/Employee_Reports_wi52/Yuvashanth Somasuntharam kukasuthan Q0560.xlsx
+++ b/Employee_Reports_wi52/Yuvashanth Somasuntharam kukasuthan Q0560.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-70</v>
+        <v>-78</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-84</v>
+        <v>-92</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-71</v>
+        <v>-79</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-322</v>
+        <v>-330</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-168</v>
+        <v>-176</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-114</v>
+        <v>-122</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-168</v>
+        <v>-176</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1501,115 +1501,115 @@
       <c r="K22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="H23" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>01-Oct-2025</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>728</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>VALID</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>01-Oct-2025</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>01-Oct-2026</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>IS0 55001 (Other Trainings)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>26-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>26-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1634,11 +1634,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
